--- a/guru99_automation/src/test/resources/testdata/DepositData.xlsx
+++ b/guru99_automation/src/test/resources/testdata/DepositData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\wipro_capstone\guru99_capstone\guru99_automation\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF3900E7-BBE5-4428-AC1E-213234BEAA9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5852C8AC-474C-4AB0-A3A8-F03F64612C18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="2685" windowWidth="15375" windowHeight="7785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4545" yWindow="1935" windowWidth="15375" windowHeight="7785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DepositData" sheetId="1" r:id="rId1"/>
@@ -394,10 +394,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>184027</v>
+        <v>184459</v>
       </c>
       <c r="B2">
-        <v>5000</v>
+        <v>24000</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -422,7 +422,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>184027</v>
+        <v>184459</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
